--- a/data/婴幼儿辅食清单100种+.xlsx
+++ b/data/婴幼儿辅食清单100种+.xlsx
@@ -4070,638 +4070,1406 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">18月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">家常软饭</t>
+          <t xml:space="preserve">二米粥（大米+小米）</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">大米/杂粮</t>
+          <t xml:space="preserve">大米、小米</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">软饭可混少量杂粮，颗粒适中。</t>
+          <t xml:space="preserve">大米小米按1:1淘洗，加水熬至软烂开花，可略稠。</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">逐步接近成人饭软度；清淡。</t>
+          <t xml:space="preserve">★崔玉涛13–24月主食；颗粒3–5mm，逐步替代糊状。</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">18月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄炒蛋</t>
+          <t xml:space="preserve">冬瓜丁（煮软·手指食物）</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄、蛋</t>
+          <t xml:space="preserve">冬瓜</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄炒蛋少油少盐。</t>
+          <t xml:space="preserve">冬瓜去皮去籽切小丁，蒸熟至筷子可透。</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1岁后极少量盐；蛋全熟。</t>
+          <t xml:space="preserve">★清淡利尿；作手指食物练抓握，初期软烂。</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">18月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">清炒时蔬</t>
+          <t xml:space="preserve">奶酪条</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">应季蔬菜</t>
+          <t xml:space="preserve">宝宝奶酪（低钠）</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">蔬菜切小段少油清炒软。</t>
+          <t xml:space="preserve">取低钠奶酪切小条直接给。</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">保留营养；软嫩。</t>
+          <t xml:space="preserve">★补钙优质脂肪；选无添加糖盐的低钠奶酪，适量。</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">18月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">蒸蛋饺</t>
+          <t xml:space="preserve">木瓜泥</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">蛋、肉馅</t>
+          <t xml:space="preserve">木瓜</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">蛋皮包肉馅蒸熟。</t>
+          <t xml:space="preserve">木瓜去皮去籽，熟透后刮泥或蒸熟打泥。</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">肉馅细；全熟。</t>
+          <t xml:space="preserve">★助消化通便；选熟软木瓜，初次少量。</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">18月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">水果酸奶杯</t>
+          <t xml:space="preserve">橙子（去籽压碎）</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">酸奶、水果</t>
+          <t xml:space="preserve">橙子</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">原味酸奶配切丁水果。</t>
+          <t xml:space="preserve">橙子去皮去籽取肉，压碎去膜。</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">无糖原味；水果小丁。</t>
+          <t xml:space="preserve">★富VC；去籽去膜防呛，1岁后适量。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">18月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">豆腐脑（少盐）</t>
+          <t xml:space="preserve">清蒸鲈鱼</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">嫩豆腐、菜</t>
+          <t xml:space="preserve">鲈鱼</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">豆腐脑淋少量生抽葱花菜。</t>
+          <t xml:space="preserve">鲈鱼段蒸熟，仔细去刺拆肉。</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1岁后极少量盐/生抽；嫩。</t>
+          <t xml:space="preserve">★少刺优质鱼；彻底去刺，富蛋白与DHA。</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">18月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">燕麦牛奶粥</t>
+          <t xml:space="preserve">煮软胡萝卜条（手指食物）</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">燕麦、奶</t>
+          <t xml:space="preserve">胡萝卜</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">燕麦煮烂加奶。</t>
+          <t xml:space="preserve">胡萝卜切粗条蒸熟至软。</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">燕麦煮软；奶温不烫。</t>
+          <t xml:space="preserve">★手指食物练咀嚼；蒸熟更软防噎。</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">18月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">鸡肉丸子汤</t>
+          <t xml:space="preserve">胡萝卜丁（煮软）</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">鸡肉、蔬菜</t>
+          <t xml:space="preserve">胡萝卜</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">鸡肉丸煮汤加菜。</t>
+          <t xml:space="preserve">胡萝卜去皮切小丁蒸熟。</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">丸子一口大小；汤去油。</t>
+          <t xml:space="preserve">★富β-胡萝卜素；少量油烹调助吸收。</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">18月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">蔬菜鸡蛋羹</t>
+          <t xml:space="preserve">番茄蛋羹</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">蛋、蔬菜</t>
+          <t xml:space="preserve">番茄、鸡蛋</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">蔬菜碎拌蛋液蒸羹。</t>
+          <t xml:space="preserve">番茄去皮去籽煮烂铺底，淋蛋液蒸成羹。</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">嫩滑；菜碎匀。</t>
+          <t xml:space="preserve">★开胃补蛋白；番茄去皮减酸，蛋全熟。</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">20月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">迷你水饺</t>
+          <t xml:space="preserve">番茄豆腐软饭</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">肉/菜、皮</t>
+          <t xml:space="preserve">番茄、豆腐、米饭</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">包小饺煮熟。</t>
+          <t xml:space="preserve">番茄煮烂，豆腐切碎拌软饭同焖软。</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">一口大小；全熟。</t>
+          <t xml:space="preserve">★植物蛋白+维C；饭软烂。</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">20月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">杂粮软粥</t>
+          <t xml:space="preserve">番茄鸡蛋软饭</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">多种杂粮</t>
+          <t xml:space="preserve">番茄、鸡蛋、米饭</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">杂粮泡发煮软烂粥。</t>
+          <t xml:space="preserve">番茄炒蛋拌软饭。</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">杂粮适量易消化；煮透。</t>
+          <t xml:space="preserve">★开胃主食；1岁后极少量盐。</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">20月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">清蒸虾</t>
+          <t xml:space="preserve">瘦肉青菜粥</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">鲜虾</t>
+          <t xml:space="preserve">瘦猪肉、青菜、大米</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">虾去线蒸熟，去壳取肉。</t>
+          <t xml:space="preserve">瘦肉剁末煮粥，青菜焯水切碎后下。</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">去壳去线；鲜虾现做。</t>
+          <t xml:space="preserve">★补铁组合；肉末细、菜须焯水。</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">20月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">肉末蒸茄子</t>
+          <t xml:space="preserve">蒸土豆块（手指食物）</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">茄子、肉末</t>
+          <t xml:space="preserve">土豆</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">茄子蒸软拌炒肉末。</t>
+          <t xml:space="preserve">土豆去皮切块蒸熟至软。</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">茄子软烂；肉末细。</t>
+          <t xml:space="preserve">★手指食物；软糯防噎。</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">20月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">蔬菜鸡蛋炒面</t>
+          <t xml:space="preserve">蒸红薯块</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">面、蛋、蔬菜</t>
+          <t xml:space="preserve">红薯</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">软面与蛋菜少油炒。</t>
+          <t xml:space="preserve">红薯去皮切块蒸熟。</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">面软剪短；清淡。</t>
+          <t xml:space="preserve">★通便；蒸熟软，初期少量防胀气。</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">22月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">什锦炒饭</t>
+          <t xml:space="preserve">蒸山药块（手指食物）</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">饭、蛋、肉、菜</t>
+          <t xml:space="preserve">山药</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">多种食材切丁炒饭。</t>
+          <t xml:space="preserve">山药去皮切块蒸熟。</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">食材小丁；少油盐。</t>
+          <t xml:space="preserve">★健脾；处理戴手套防痒，软块防噎。</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">22月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄菌菇汤</t>
+          <t xml:space="preserve">草莓（压碎）</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄、菌菇</t>
+          <t xml:space="preserve">草莓</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄菌菇煮汤。</t>
+          <t xml:space="preserve">草莓洗净去蒂压碎。</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">菌菇切碎熟透；清淡。</t>
+          <t xml:space="preserve">★富VC；彻底清洗去农残，1岁后适量。</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">22月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">软煎三文鱼</t>
+          <t xml:space="preserve">菠菜蛋羹</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">三文鱼</t>
+          <t xml:space="preserve">菠菜、鸡蛋</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">三文鱼少油煎熟去刺。</t>
+          <t xml:space="preserve">菠菜焯水切碎拌蛋液蒸羹。</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">中心熟透；去刺。</t>
+          <t xml:space="preserve">★补铁+蛋白；菠菜必焯水去草酸。</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">22月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">南瓜小米饭</t>
+          <t xml:space="preserve">西兰花碎（手指食物）</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">南瓜、小米、米</t>
+          <t xml:space="preserve">西兰花</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">南瓜小米与米同煮。</t>
+          <t xml:space="preserve">西兰花掰小朵焯熟，撕/切细碎。</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">软饭；南瓜甜软。</t>
+          <t xml:space="preserve">★富维C叶酸；作手指食物，软烂。</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">18–24月（接近成人）</t>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">24月起</t>
+          <t xml:space="preserve">13月起</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">蔬菜鸡肉卷</t>
+          <t xml:space="preserve">西葫芦丁</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">鸡肉、蔬菜</t>
+          <t xml:space="preserve">西葫芦</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">鸡肉泥裹蔬菜蒸卷切块。</t>
+          <t xml:space="preserve">西葫芦去皮切小丁，蒸熟或少油炒软。</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">卷紧切块；全熟。</t>
+          <t xml:space="preserve">★清淡低敏；软嫩。</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13月起</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豆腐羹</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">嫩豆腐、青菜</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豆腐焯水打碎，加菜碎勾薄羹。</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★植物蛋白；焯水去豆腥。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13月起</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">青菜肉末软饭</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">青菜、猪肉末、米饭</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">肉末炒熟拌青菜碎与软饭。</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★荤素主食；饭软、肉末细。</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13月起</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">香菇碎</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">香菇</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">香菇切碎煮熟。</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★提鲜补微量；切碎熟透，初次少量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13月起</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蛋黄羹</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸡蛋黄</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蛋黄加温水打散蒸羹。</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★蛋黄铁+卵磷脂；由1/4个起，蛋白1岁后。</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12–18月（家庭软食）</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13月起</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蔬菜鸡肉粥</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸡肉、多种蔬菜、大米</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸡肉蔬菜剁末同煮粥软烂。</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★优质蛋白；食材切碎，清淡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t xml:space="preserve">18–24月（接近成人）</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18月起</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">家常软饭</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大米/杂粮</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">软饭可混少量杂粮，颗粒适中。</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">逐步接近成人饭软度；清淡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18月起</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">番茄炒蛋</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">番茄、蛋</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">番茄炒蛋少油少盐。</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1岁后极少量盐；蛋全熟。</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18月起</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">清炒时蔬</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">应季蔬菜</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蔬菜切小段少油清炒软。</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">保留营养；软嫩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18月起</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蒸蛋饺</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蛋、肉馅</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蛋皮包肉馅蒸熟。</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">肉馅细；全熟。</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18月起</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水果酸奶杯</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">酸奶、水果</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原味酸奶配切丁水果。</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无糖原味；水果小丁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18月起</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豆腐脑（少盐）</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">嫩豆腐、菜</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">豆腐脑淋少量生抽葱花菜。</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1岁后极少量盐/生抽；嫩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18月起</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">燕麦牛奶粥</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">燕麦、奶</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">燕麦煮烂加奶。</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">燕麦煮软；奶温不烫。</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18月起</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸡肉丸子汤</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸡肉、蔬菜</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸡肉丸煮汤加菜。</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">丸子一口大小；汤去油。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18月起</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蔬菜鸡蛋羹</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蛋、蔬菜</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蔬菜碎拌蛋液蒸羹。</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">嫩滑；菜碎匀。</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20月起</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">迷你水饺</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">肉/菜、皮</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">包小饺煮熟。</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一口大小；全熟。</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20月起</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杂粮软粥</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">多种杂粮</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杂粮泡发煮软烂粥。</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">杂粮适量易消化；煮透。</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20月起</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">清蒸虾</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鲜虾</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">虾去线蒸熟，去壳取肉。</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">去壳去线；鲜虾现做。</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20月起</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">肉末蒸茄子</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">茄子、肉末</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">茄子蒸软拌炒肉末。</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">茄子软烂；肉末细。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20月起</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蔬菜鸡蛋炒面</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">面、蛋、蔬菜</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">软面与蛋菜少油炒。</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">面软剪短；清淡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22月起</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">什锦炒饭</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">饭、蛋、肉、菜</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">多种食材切丁炒饭。</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">食材小丁；少油盐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22月起</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">番茄菌菇汤</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">番茄、菌菇</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">番茄菌菇煮汤。</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">菌菇切碎熟透；清淡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22月起</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">软煎三文鱼</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三文鱼</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三文鱼少油煎熟去刺。</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中心熟透；去刺。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22月起</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南瓜小米饭</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南瓜、小米、米</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南瓜小米与米同煮。</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">软饭；南瓜甜软。</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
         <is>
           <t xml:space="preserve">24月起</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蔬菜鸡肉卷</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸡肉、蔬菜</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸡肉泥裹蔬菜蒸卷切块。</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卷紧切块；全熟。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18–24月（接近成人）</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24月起</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
         <is>
           <t xml:space="preserve">杂蔬软饼</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t xml:space="preserve">多种蔬菜、面、蛋</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t xml:space="preserve">蔬菜碎拌面蛋摊软饼。</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t xml:space="preserve">蔬菜丰富；软嫩。</t>
         </is>
